--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -440,11 +440,7 @@
     <col width="38" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,26 +486,6 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>响应时间阈值ms</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>超时时间秒</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>轮询间隔秒</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>连续失败告警次数</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
           <t>通知组</t>
         </is>
       </c>
@@ -555,19 +531,7 @@
           <t>status=200</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
         </is>
@@ -614,19 +578,7 @@
           <t>status=200; code=0</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
         </is>

--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://qyapi.weixin.qq.com/cgi-bin/webhook/send?key=替换成你的key</t>
+          <t>https://qyapi.weixin.qq.com/cgi-bin/webhook/send?key=REPLACE_WITH_YOUR_KEY</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">

--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -441,6 +441,8 @@
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +488,16 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>轮询间隔ms</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>超时时间ms</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>通知组</t>
         </is>
       </c>
@@ -531,7 +543,13 @@
           <t>status=200</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
         </is>
@@ -578,7 +596,13 @@
           <t>status=200; code=0</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
         </is>

--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>轮询间隔ms</t>
+          <t>轮询间隔秒</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>5000</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3600000</v>
+        <v>3600</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>5000</v>

--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -441,8 +441,9 @@
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,10 +494,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>异常后轮询间隔秒</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>超时时间ms</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>通知组</t>
         </is>
@@ -547,9 +553,12 @@
         <v>3600</v>
       </c>
       <c r="J2" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="K2" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
         </is>
@@ -600,9 +609,12 @@
         <v>3600</v>
       </c>
       <c r="J3" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="K3" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
         </is>

--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -695,13 +695,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -712,15 +714,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>企业微信Webhook</t>
+          <t>Webhook地址</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>通知类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>签名密钥</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>是否@所有人</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -739,12 +751,18 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>企业微信</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>企业微信群机器人 webhook</t>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>企业微信或飞书群机器人 webhook</t>
         </is>
       </c>
     </row>

--- a/config/巡检配置_示例.xlsx
+++ b/config/巡检配置_示例.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="巡检接口" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前置变量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前置请求" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前置变量" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="通知配置" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -444,6 +445,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,6 +509,11 @@
           <t>通知组</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>前置请求</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -563,6 +570,7 @@
           <t>默认组</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -577,7 +585,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>业务状态</t>
+          <t>需要登录的业务状态</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -592,12 +600,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>{"Authorization":"Bearer ${token}","Content-Type":"application/json"}</t>
+          <t>{"Content-Type":"application/json"}</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>{"bizId":"DEMO-001"}</t>
+          <t>{"ticketid":"${ticketid}"}</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -617,6 +625,72 @@
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>默认组</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>登录刷新ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>示例巡检</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>派生参数业务查询</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://api.example.test/member/coupon</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>{"Content-Type":"application/json"}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>{"memberId":"${member_id}"}</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>status=200; code=0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>默认组</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>登录刷新ticket,会员详情取memberId</t>
         </is>
       </c>
     </row>
@@ -631,7 +705,169 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>是否启用</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>前置名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>请求方式</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>请求头JSON</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>请求参数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>成功判断</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>提取变量JSON</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>超时时间ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>登录刷新ticket</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://api.example.test/login</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{"Content-Type":"application/json"}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>{"openid":"${openid}","unionid":"${unionid}"}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>status=200; code=0</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>{"ticketid":"data.ticketid","app_user_id":"data.useruuid","phone":"data.phone"}</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>会员详情取memberId</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://api.example.test/member/detail</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{"Content-Type":"application/json"}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>{"appId":"${app_user_id}"}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>status=200; code=0</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>{"member_id":"data.memId"}</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -665,12 +901,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>token</t>
+          <t>openid</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>demo-token</t>
+          <t>demo-openid</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -680,7 +916,29 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>示例变量，真实 token 不要提交到 git</t>
+          <t>登录前置请求入参，真实 openid 不要提交到 git</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>unionid</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>demo-unionid</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>登录前置请求入参，真实 unionid 不要提交到 git</t>
         </is>
       </c>
     </row>
@@ -689,7 +947,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
